--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:27</t>
+          <t>2026-09-01 03:16:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:28</t>
+          <t>2026-09-01 03:16:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:29</t>
+          <t>2026-09-01 03:16:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:31</t>
+          <t>2026-09-01 03:16:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:31</t>
+          <t>2026-09-01 03:16:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:31</t>
+          <t>2026-09-01 03:16:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:31</t>
+          <t>2026-09-01 03:16:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:10:31</t>
+          <t>2026-09-01 03:16:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:21</t>
+          <t>2026-09-01 03:33:04</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:23</t>
+          <t>2026-09-01 03:33:05</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:24</t>
+          <t>2026-09-01 03:33:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:16:25</t>
+          <t>2026-09-01 03:33:08</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.41%6100</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>6100</v>
+        <v>5995</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+3.54%5990</t>
+          <t>-1.75%5885</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+3.54%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>5990</v>
+        <v>5885</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.61%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-10%999</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-10%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>999</v>
+        <v>971</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.61%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-3.98%2170</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.98%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2170</v>
+        <v>2315</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5130</v>
+        <v>5410</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.1%1165</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.1%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1165</v>
+        <v>1225</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>+0.30%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>16065</v>
+        <v>17120</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.19%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-9.71%5860</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5860</v>
+        <v>5870</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+6.16%2845</t>
+          <t>+9.84%3125</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+6.16%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2845</v>
+        <v>3125</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:04</t>
+          <t>2026-09-01 15:29:32</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.58%927</t>
+          <t>+3.34%958</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.58%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+3.65%539</t>
+          <t>+0.93%544</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+3.65%</t>
+          <t>+0.93%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>539</v>
+        <v>544</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.71%2305</t>
+          <t>-0.87%2285</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.71%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2305</v>
+        <v>2285</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+6.81%3530</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>3530</v>
+        <v>3425</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-5.68%2825</t>
+          <t>+1.95%2880</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-5.68%</t>
+          <t>+1.95%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>2825</v>
+        <v>2880</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.73%646</t>
+          <t>-3.25%625</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.73%</t>
+          <t>-3.25%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>646</v>
+        <v>625</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-3.02%2410</t>
+          <t>+2.9%2480</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-3.02%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2410</v>
+        <v>2480</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H27" t="n">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-0.99%199.5</t>
+          <t>+0.25%200</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-0.99%</t>
+          <t>+0.25%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>199.5</v>
+        <v>200</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.47%1345</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1345</v>
+        <v>1375</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.55%1840</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.55%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1840</v>
+        <v>1865</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:05</t>
+          <t>2026-09-01 15:29:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.12%969</t>
+          <t>+2.17%990</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.12%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>969</v>
+        <v>990</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-0.32%618</t>
+          <t>-1.46%609</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+0.56%6285</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+0.56%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6285</v>
+        <v>6910</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.17%912</t>
+          <t>+8.99%994</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-6.17%</t>
+          <t>+8.99%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.21%244</t>
+          <t>+2.05%249</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.21%</t>
+          <t>+2.05%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-2.1%607</t>
+          <t>+9.88%667</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>+9.88%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>607</v>
+        <v>667</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-2.66%769</t>
+          <t>+3.9%799</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-2.66%</t>
+          <t>+3.9%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>769</v>
+        <v>799</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.98%151.5</t>
+          <t>+1.32%153.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+1.32%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>151.5</v>
+        <v>153.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.23%216.5</t>
+          <t>+6.47%230.5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+6.47%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>216.5</v>
+        <v>230.5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.81%257</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.77%129</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>129</v>
+        <v>132.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-1.72%741</t>
+          <t>+2.7%761</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>+2.7%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-2.98%228</t>
+          <t>+4.17%237.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-2.98%</t>
+          <t>+4.17%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>228</v>
+        <v>237.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.19%435</t>
+          <t>+3.45%450</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.19%</t>
+          <t>+3.45%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.25%4075</t>
+          <t>+4.91%4275</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+4.91%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>4075</v>
+        <v>4275</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:06</t>
+          <t>2026-09-01 15:29:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.2%677</t>
+          <t>+5.02%711</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+5.02%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:08</t>
+          <t>2026-09-01 15:29:36</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:08</t>
+          <t>2026-09-01 15:29:36</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.59%1690</t>
+          <t>+3.25%1745</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+3.25%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1690</v>
+        <v>1745</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:08</t>
+          <t>2026-09-01 15:29:36</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.71%1425</t>
+          <t>+1.4%1445</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.71%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1425</v>
+        <v>1445</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:08</t>
+          <t>2026-09-01 15:29:36</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-8.61%1380</t>
+          <t>+7.25%1480</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.61%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1380</v>
+        <v>1480</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:33:08</t>
+          <t>2026-09-01 15:29:36</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-3.21%241</t>
+          <t>+5.81%255</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-3.21%</t>
+          <t>+5.81%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:32</t>
+          <t>2026-09-01 15:57:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:34</t>
+          <t>2026-09-01 15:57:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:35</t>
+          <t>2026-09-01 15:57:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:36</t>
+          <t>2026-09-01 15:57:22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:36</t>
+          <t>2026-09-01 15:57:22</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:36</t>
+          <t>2026-09-01 15:57:22</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:36</t>
+          <t>2026-09-01 15:57:22</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:29:36</t>
+          <t>2026-09-01 15:57:22</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:18</t>
+          <t>2026-09-01 16:17:33</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:19</t>
+          <t>2026-09-01 16:17:34</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:21</t>
+          <t>2026-09-01 16:17:36</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:22</t>
+          <t>2026-09-01 16:17:37</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:22</t>
+          <t>2026-09-01 16:17:37</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:22</t>
+          <t>2026-09-01 16:17:37</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:22</t>
+          <t>2026-09-01 16:17:37</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:57:22</t>
+          <t>2026-09-01 16:17:37</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7.90%658,000</t>
+          <t>7.71%658,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.90%</t>
+          <t>7.71%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.78%364,000</t>
+          <t>7.50%364,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.78%</t>
+          <t>7.50%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.76%370,000</t>
+          <t>7.48%370,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.76%</t>
+          <t>7.48%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>6.60%480,000</t>
+          <t>7.12%480,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6.60%</t>
+          <t>7.12%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.61%</t>
+          <t>+0.66%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>971</v>
+        <v>2315</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.49%1,570,000</t>
+          <t>5.29%665,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.49%</t>
+          <t>5.29%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>1570000</v>
+        <v>665000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.16%</t>
+          <t>+0.34%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2315</v>
+        <v>971</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.06%665,000</t>
+          <t>5.24%1,570,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.06%</t>
+          <t>5.24%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>665000</v>
+        <v>1570000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-0.15%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.91%273,000</t>
+          <t>5.08%273,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.91%</t>
+          <t>5.08%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.60%1,127,000</t>
+          <t>4.74%1,127,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.60%</t>
+          <t>4.74%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.07%212,000</t>
+          <t>4.11%212,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.11%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.77%529,000</t>
+          <t>4.01%529,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.32%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1225</v>
+        <v>17120</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.18%739,000</t>
+          <t>3.19%54,300</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.18%</t>
+          <t>3.19%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>739000</v>
+        <v>54300</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.20%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>17120</v>
+        <v>1225</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.06%54,300</t>
+          <t>3.11%739,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>54300</v>
+        <v>739000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>+9.84%3125</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+9.84%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>5870</v>
+        <v>3125</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.46%120,000</t>
+          <t>2.63%245,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.63%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>120000</v>
+        <v>245000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+9.84%3125</t>
+          <t>+3.34%958</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+9.84%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>3125</v>
+        <v>958</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.44%245,000</t>
+          <t>2.47%750,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>245000</v>
+        <v>750000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:33</t>
+          <t>2026-09-01 19:38:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+3.34%958</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+3.34%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>958</v>
+        <v>5870</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.44%750,000</t>
+          <t>2.42%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>750000</v>
+        <v>120000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.27%1,200,000</t>
+          <t>2.24%1,200,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.24%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.19%271,000</t>
+          <t>2.13%271,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.13%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2.09%42,000</t>
+          <t>2.04%42,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.04%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.96%158,400</t>
+          <t>1.86%158,400</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.54%306,000</t>
+          <t>1.52%306,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.51%179,000</t>
+          <t>1.50%179,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.47%650,000</t>
+          <t>1.40%650,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3131弘塑</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.9%2480</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.9%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2480</v>
+        <v>7800</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.28%152,000</t>
+          <t>1.34%50,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.28%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>152000</v>
+        <v>50000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>3131弘塑</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>+2.9%2480</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.9%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>7800</v>
+        <v>2480</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.24%50,000</t>
+          <t>1.30%152,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.30%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>50000</v>
+        <v>152000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.16%282,000</t>
+          <t>1.14%282,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.98%1,400,000</t>
+          <t>0.96%1,400,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.96%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2169,12 +2169,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.93%198,000</t>
+          <t>0.94%198,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.93%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.61%94,000</t>
+          <t>0.60%94,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:34</t>
+          <t>2026-09-01 19:38:14</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6831邁科</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.46%609</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>609</v>
+        <v>6910</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.54%250,000</t>
+          <t>0.55%23,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.55%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>250000</v>
+        <v>23000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6831邁科</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.94%6910</t>
+          <t>-1.46%609</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>6910</v>
+        <v>609</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.51%23,000</t>
+          <t>0.52%250,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.52%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>23000</v>
+        <v>250000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.35%110,000</t>
+          <t>0.38%110,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.31%146,000</t>
+          <t>0.33%146,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.31%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2779,12 +2779,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.05%72,000</t>
+          <t>0.06%72,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:36</t>
+          <t>2026-09-01 19:38:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:37</t>
+          <t>2026-09-01 19:38:16</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:37</t>
+          <t>2026-09-01 19:38:16</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:37</t>
+          <t>2026-09-01 19:38:16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1590亞德客-KY</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+1.4%1445</t>
+          <t>+7.25%1480</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+1.4%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1445</v>
+        <v>1480</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:37</t>
+          <t>2026-09-01 19:38:16</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>1590亞德客-KY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+7.25%1480</t>
+          <t>+1.4%1445</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>+1.4%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>1480</v>
+        <v>1445</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 16:17:37</t>
+          <t>2026-09-01 19:38:16</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:13</t>
+          <t>2026-09-01 20:36:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:14</t>
+          <t>2026-09-01 20:36:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:15</t>
+          <t>2026-09-01 20:36:06</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:16</t>
+          <t>2026-09-01 20:36:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:16</t>
+          <t>2026-09-01 20:36:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:16</t>
+          <t>2026-09-01 20:36:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:16</t>
+          <t>2026-09-01 20:36:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 19:38:16</t>
+          <t>2026-09-01 20:36:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
